--- a/demo_B/バス停緯度経度時刻.xlsx
+++ b/demo_B/バス停緯度経度時刻.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nahasyakyo.sharepoint.com/sites/documentsites/Share/◎地域福祉課総合/★★生活支援体制整備事業/★★★資源一覧/map/アプリ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\社会福祉法人那覇市社会福祉協議会\ドキュメント管理サイト - Share\◎地域福祉課総合\★★生活支援体制整備事業\★★★資源一覧\map\アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1013" documentId="8_{4B447A0D-3F0B-4324-8CE0-0305766AF75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{202FE4E8-6380-4B39-9D8C-1A9BDAC45B55}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE028521-D0C7-4E42-BD2E-2ACEC4B5DEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12720" yWindow="0" windowWidth="15555" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="本庁1・2・3・4便" sheetId="13" r:id="rId1"/>
-    <sheet name="首里1・2・3・4" sheetId="14" r:id="rId2"/>
+    <sheet name="首里1・2・3・4便" sheetId="14" r:id="rId2"/>
     <sheet name="真和志1・2便" sheetId="15" r:id="rId3"/>
     <sheet name="真和志3・4便" sheetId="16" r:id="rId4"/>
     <sheet name="小禄1・2便" sheetId="17" r:id="rId5"/>
@@ -5218,26 +5218,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="55c5442c-bee5-4401-964a-30a8edf90fbf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="84d7fb4b-e177-4e05-b007-8554f2896fad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101002BFE28831A6D794EB075823C428B55FF" ma:contentTypeVersion="14" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="34e4bae747e2ff9445c0efe2e38baa76">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="55c5442c-bee5-4401-964a-30a8edf90fbf" xmlns:ns3="84d7fb4b-e177-4e05-b007-8554f2896fad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fda2398280d22e90703e4f7fdbca0175" ns2:_="" ns3:_="">
     <xsd:import namespace="55c5442c-bee5-4401-964a-30a8edf90fbf"/>
@@ -5450,10 +5430,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="55c5442c-bee5-4401-964a-30a8edf90fbf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="84d7fb4b-e177-4e05-b007-8554f2896fad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B3264A-BBB8-4932-A6AB-4107620005FA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF44372-46B8-4328-8F27-D6CB7F87E916}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="55c5442c-bee5-4401-964a-30a8edf90fbf"/>
+    <ds:schemaRef ds:uri="84d7fb4b-e177-4e05-b007-8554f2896fad"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5470,20 +5481,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF44372-46B8-4328-8F27-D6CB7F87E916}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B3264A-BBB8-4932-A6AB-4107620005FA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="55c5442c-bee5-4401-964a-30a8edf90fbf"/>
-    <ds:schemaRef ds:uri="84d7fb4b-e177-4e05-b007-8554f2896fad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>